--- a/results/07-2026/beta/contributions-comparison-07-2026.xlsx
+++ b/results/07-2026/beta/contributions-comparison-07-2026.xlsx
@@ -2788,16 +2788,16 @@
         <v>0.445899379286268</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.172652474863118</v>
+        <v>-0.0273475251368821</v>
       </c>
       <c r="AD23" t="n">
         <v>-0.491452879857937</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.2331894038576</v>
+        <v>-0.4331894038576</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.046173352173961</v>
+        <v>-0.00382664782603898</v>
       </c>
     </row>
     <row r="24">
@@ -2895,7 +2895,7 @@
         <v>0.26031492736318</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.039150923320437</v>
+        <v>-0.089150923320437</v>
       </c>
     </row>
     <row r="25">
@@ -2993,7 +2993,7 @@
         <v>-1.22424133666683</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.473042371556266</v>
+        <v>-0.523042371556266</v>
       </c>
     </row>
     <row r="26">
@@ -3082,16 +3082,16 @@
         <v>-0.0696095758028083</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.386162553483636</v>
+        <v>0.446162553483636</v>
       </c>
       <c r="AD26" t="n">
         <v>0.143565841710704</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.758904077301381</v>
+        <v>0.818904077301381</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.109552933964968</v>
+        <v>-0.144552933964968</v>
       </c>
     </row>
     <row r="27">
@@ -3180,16 +3180,16 @@
         <v>-0.393041613759915</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.274423756613508</v>
+        <v>0.334423756613508</v>
       </c>
       <c r="AD27" t="n">
         <v>0.417671871417178</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.218459489374329</v>
+        <v>-0.158459489374329</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.10587045534415</v>
+        <v>-0.0758704553441498</v>
       </c>
     </row>
     <row r="28">
@@ -3278,16 +3278,16 @@
         <v>-0.0388741365488032</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.00270540138671922</v>
+        <v>0.0627054013867192</v>
       </c>
       <c r="AD28" t="n">
         <v>-0.0357858960579702</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.480129880866155</v>
+        <v>-0.420129880866155</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.290981657401484</v>
+        <v>-0.245981657401484</v>
       </c>
     </row>
     <row r="29">
@@ -3376,16 +3376,16 @@
         <v>-0.00921784082785182</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.222168421360049</v>
+        <v>-0.162168421360049</v>
       </c>
       <c r="AD29" t="n">
         <v>-0.161029071650163</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.53110091196003</v>
+        <v>-0.47110091196003</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.117696551224783</v>
+        <v>-0.0576965512247833</v>
       </c>
     </row>
     <row r="30">
@@ -3474,16 +3474,16 @@
         <v>0.062322220140975</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.525330027874355</v>
+        <v>-0.465330027874355</v>
       </c>
       <c r="AD30" t="n">
         <v>-0.323163577136945</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.827244906389214</v>
+        <v>-0.767244906389214</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.514233797147432</v>
+        <v>-0.454233797147432</v>
       </c>
     </row>
     <row r="31">
@@ -3572,16 +3572,16 @@
         <v>-0.0452037874837307</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.583530017202277</v>
+        <v>-0.523530017202277</v>
       </c>
       <c r="AD31" t="n">
         <v>-0.176968014107152</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.863692124588244</v>
+        <v>-0.803692124588244</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.675541955950911</v>
+        <v>-0.615541955950911</v>
       </c>
     </row>
     <row r="32">
@@ -3679,7 +3679,7 @@
         <v>-0.690644749508038</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.728170673111381</v>
+        <v>-0.683170673111381</v>
       </c>
     </row>
     <row r="33">
@@ -3777,7 +3777,7 @@
         <v>-0.689793416877435</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.767843799340733</v>
+        <v>-0.737843799340733</v>
       </c>
     </row>
     <row r="34">
@@ -3875,7 +3875,7 @@
         <v>-0.783675786582959</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.756951519389169</v>
+        <v>-0.741951519389169</v>
       </c>
     </row>
     <row r="35">
@@ -6229,16 +6229,16 @@
         <v>0.445899379286268</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.0273475251368821</v>
+        <v>0.172652474863118</v>
       </c>
       <c r="AD23" t="n">
         <v>-0.491452879857937</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.4331894038576</v>
+        <v>-0.2331894038576</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.00382664782603898</v>
+        <v>0.046173352173961</v>
       </c>
     </row>
     <row r="24">
@@ -6336,7 +6336,7 @@
         <v>0.26031492736318</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.089150923320437</v>
+        <v>-0.039150923320437</v>
       </c>
     </row>
     <row r="25">
@@ -6434,7 +6434,7 @@
         <v>-1.22424133666683</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.523042371556266</v>
+        <v>-0.473042371556266</v>
       </c>
     </row>
     <row r="26">
@@ -6460,7 +6460,7 @@
         <v>0.0615892555664469</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0280940604383807</v>
+        <v>-0.0356256342358478</v>
       </c>
       <c r="I26" t="n">
         <v>0.311873561435571</v>
@@ -6517,22 +6517,22 @@
         <v>-0.0840539218205656</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.518830766937432</v>
+        <v>0.455439403146275</v>
       </c>
       <c r="AB26" t="n">
         <v>-0.0696095758028083</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.509600270732323</v>
+        <v>0.386162553483636</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.206957205501861</v>
+        <v>0.143565841710704</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.882341794550067</v>
+        <v>0.758904077301381</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.128693504652796</v>
+        <v>-0.109552933964968</v>
       </c>
     </row>
     <row r="27">
@@ -6540,37 +6540,37 @@
         <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.245828091669527</v>
+        <v>-0.390051949495858</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.177275710542129</v>
+        <v>-0.10283129649198</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0934153245580765</v>
+        <v>0.24880917722511</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0296502192522053</v>
+        <v>0.044061547646663</v>
       </c>
       <c r="H27" t="n">
-        <v>0.15066071707793</v>
+        <v>0.120615333084993</v>
       </c>
       <c r="I27" t="n">
-        <v>0.251468688589652</v>
+        <v>0.247130756577631</v>
       </c>
       <c r="J27" t="n">
-        <v>0.00231154438498049</v>
+        <v>0.00573683451412558</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.374765563894696</v>
+        <v>-0.459941198175216</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.0260967169117653</v>
+        <v>-0.0407440450786525</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -6582,55 +6582,55 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.00928020631317775</v>
+        <v>-0.0129006585413489</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.00643580221621936</v>
+        <v>-0.00124023538831508</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.00223445309594039</v>
+        <v>-0.00231638452737498</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.00981883148343891</v>
+        <v>-0.0102148698544242</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.00645652916948279</v>
+        <v>-0.00672659322776395</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.00308274799129135</v>
+        <v>-0.00303504657136149</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.000501282053285915</v>
+        <v>-0.0000749382225805066</v>
       </c>
       <c r="W27" t="n">
-        <v>0.185191453373972</v>
+        <v>0.170313905042514</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0298460339594499</v>
+        <v>-0.026612380849588</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.310038277709138</v>
+        <v>-0.578910428388705</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.113065524502518</v>
+        <v>0.0860271824008671</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.467555812719875</v>
+        <v>0.664802627994809</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.210068495709401</v>
+        <v>-0.393041613759915</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.318520072724498</v>
+        <v>0.274423756613508</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.216087124130223</v>
+        <v>0.417671871417178</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.104583729487159</v>
+        <v>-0.218459489374329</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.0465420860601855</v>
+        <v>-0.10587045534415</v>
       </c>
     </row>
     <row r="28">
@@ -6644,31 +6644,31 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.305721872067719</v>
+        <v>-0.303171373054015</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.176127949318067</v>
+        <v>-0.179663909198859</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0276004019594846</v>
+        <v>-0.0781168299324413</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0281345637364049</v>
+        <v>-0.0659577518115217</v>
       </c>
       <c r="H28" t="n">
-        <v>0.153494679976479</v>
+        <v>0.108904049552824</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0779075492671008</v>
+        <v>0.0773483950142857</v>
       </c>
       <c r="J28" t="n">
-        <v>0.00115656499275171</v>
+        <v>-0.000755497453227195</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.18280391924259</v>
+        <v>-0.163557653957393</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.0251550637755173</v>
+        <v>-0.0250028202782631</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -6680,55 +6680,55 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.00980071288789747</v>
+        <v>-0.00960656584739866</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.00661162852422211</v>
+        <v>0.00318026432896983</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.00280854098034665</v>
+        <v>-0.00278837438517172</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.0066781199855861</v>
+        <v>-0.00663016700572476</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.005739381322512</v>
+        <v>-0.00569816927979955</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0042593828202296</v>
+        <v>0.00422879975491397</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.00042681498549892</v>
+        <v>-0.000489201022774359</v>
       </c>
       <c r="W28" t="n">
-        <v>0.141640446848836</v>
+        <v>0.192169067788146</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.0327728224575521</v>
+        <v>-0.0250149214786578</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.321933384762828</v>
+        <v>-0.319266472316735</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.159916436622958</v>
+        <v>-0.163568809936139</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.23190505200772</v>
+        <v>0.0415624989563154</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.11344944776243</v>
+        <v>-0.0388741365488032</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.178733291340387</v>
+        <v>0.00270540138671922</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.153997502740619</v>
+        <v>-0.0357858960579702</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.3031165300454</v>
+        <v>-0.480129880866155</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.187399950412331</v>
+        <v>-0.290981657401484</v>
       </c>
     </row>
     <row r="29">
@@ -6742,31 +6742,31 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.106115751400478</v>
+        <v>-0.10509706538087</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.199823746473653</v>
+        <v>-0.20383542521911</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0134596169475721</v>
+        <v>-0.0845458150445576</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0168163974913964</v>
+        <v>-0.0355128127356381</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0174221214404085</v>
+        <v>-0.0410218754891347</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0522762213502476</v>
+        <v>-0.0519007483582602</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00213343237140635</v>
+        <v>0.00022327963086128</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.126301044684712</v>
+        <v>-0.106948479871051</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.0268811420302011</v>
+        <v>-0.0267158696055829</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -6778,55 +6778,55 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.00931762898431908</v>
+        <v>-0.00920569005045759</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.00911864546533297</v>
+        <v>0.00593101304931727</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.000292956567298017</v>
+        <v>-0.000290853036738216</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.00302773625467992</v>
+        <v>-0.00300599570989292</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.00316356013999038</v>
+        <v>-0.00314084429935788</v>
       </c>
       <c r="U29" t="n">
-        <v>0.00862900512915728</v>
+        <v>0.00856704901296544</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.000395058935498081</v>
+        <v>-0.000416314555508507</v>
       </c>
       <c r="W29" t="n">
-        <v>0.088694124850318</v>
+        <v>0.140789039464673</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.0188333683503671</v>
+        <v>-0.0149519809080768</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.145712300878208</v>
+        <v>-0.144408923968271</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.160227196995923</v>
+        <v>-0.16452356663171</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.0629991340991395</v>
+        <v>-0.212929820008423</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.0816728725013126</v>
+        <v>-0.00921784082785182</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.0847264715812518</v>
+        <v>-0.222168421360049</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.0107229127488918</v>
+        <v>-0.161029071650163</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.390665969455383</v>
+        <v>-0.53110091196003</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.0209938913905315</v>
+        <v>-0.117696551224783</v>
       </c>
     </row>
     <row r="30">
@@ -6840,31 +6840,31 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.113164913190188</v>
+        <v>-0.112078556891</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.18610015880645</v>
+        <v>-0.189836321623858</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.253688552873603</v>
+        <v>-0.257587029874378</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0163834111471112</v>
+        <v>-0.0348063492509894</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0273890339335365</v>
+        <v>-0.030278032200964</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.266796072615499</v>
+        <v>-0.264877461146676</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00244880975095944</v>
+        <v>0.000600367391673361</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.018270594207518</v>
+        <v>0.00163978916660936</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.0201007155921442</v>
+        <v>-0.0199835440579</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -6876,55 +6876,55 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.00496105405103438</v>
+        <v>-0.00488154071948282</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.00719099301896662</v>
+        <v>0.00426771805574338</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.000285887300933681</v>
+        <v>-0.000283834530230957</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.00134637223515562</v>
+        <v>-0.00133670475321812</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.00177898448095576</v>
+        <v>-0.001766210641342</v>
       </c>
       <c r="U30" t="n">
-        <v>0.00237352109977082</v>
+        <v>0.00235647864863639</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.00036558937839662</v>
+        <v>-0.00038644433387688</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0526619964893101</v>
+        <v>0.107271115385142</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.0237955709487201</v>
+        <v>-0.0246207504985642</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.140129793493637</v>
+        <v>-0.138849765025578</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.159135278503001</v>
+        <v>-0.16306511348928</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.50766973421812</v>
+        <v>-0.588041038283621</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.00865652585666954</v>
+        <v>0.062322220140975</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.456372911986712</v>
+        <v>-0.525330027874355</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.240873661602622</v>
+        <v>-0.323163577136945</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.75563798398335</v>
+        <v>-0.827244906389214</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.388501053242823</v>
+        <v>-0.514233797147432</v>
       </c>
     </row>
     <row r="31">
@@ -6938,31 +6938,31 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0968351470163008</v>
+        <v>-0.0959055525953943</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.180630207192896</v>
+        <v>-0.184256554790573</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1179177107918</v>
+        <v>-0.122875155541994</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0118967399948219</v>
+        <v>-0.0301316892296198</v>
       </c>
       <c r="H31" t="n">
-        <v>0.034355240620171</v>
+        <v>-0.0226394617934077</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.363716674946979</v>
+        <v>-0.361099619887286</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00123448926048061</v>
+        <v>-0.000567523168084753</v>
       </c>
       <c r="K31" t="n">
-        <v>0.00931952034388283</v>
+        <v>-0.0510638710772991</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.0194997457752914</v>
+        <v>-0.0193587685922786</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -6974,55 +6974,55 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.00177540513341189</v>
+        <v>-0.00153588892618246</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.00673020310747897</v>
+        <v>0.00422125413741203</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.000279525792158087</v>
+        <v>-0.000277518699373274</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.00101716580951284</v>
+        <v>-0.00100986217289995</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.00149695875046331</v>
+        <v>-0.00148620998873239</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.000323758650314936</v>
+        <v>-0.000321433949559172</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.000318364508273839</v>
+        <v>-0.000358321963792569</v>
       </c>
       <c r="W31" t="n">
-        <v>0.0605677471449163</v>
+        <v>0.0134692571511936</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.0120783940754789</v>
+        <v>0.0125106577301246</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.122605259151308</v>
+        <v>-0.12149058022018</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.15486009505789</v>
+        <v>-0.158671527165787</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.458272130010322</v>
+        <v>-0.538067633994438</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.0398427805528704</v>
+        <v>-0.0452037874837307</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.358235045105774</v>
+        <v>-0.583530017202277</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.0945554550633428</v>
+        <v>-0.176968014107152</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.635700399314971</v>
+        <v>-0.863692124588244</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.521280220699776</v>
+        <v>-0.675541955950911</v>
       </c>
     </row>
     <row r="32">
@@ -7036,31 +7036,31 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.103413937754058</v>
+        <v>-0.102421188503996</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.187907680306217</v>
+        <v>-0.191680131080941</v>
       </c>
       <c r="F32" t="n">
-        <v>0.113718617959926</v>
+        <v>0.0850787883825667</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.00842644245736131</v>
+        <v>-0.0265550894922778</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0299348951591768</v>
+        <v>-0.0264830128301241</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.386317066282201</v>
+        <v>-0.383537040711274</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0010714416803457</v>
+        <v>-0.000687081477375705</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0149296478809223</v>
+        <v>-0.0113761785131741</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.0190304178563479</v>
+        <v>-0.0188928341532532</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -7072,55 +7072,55 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.000353401565322678</v>
+        <v>0.000500264519207484</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.00622881821531735</v>
+        <v>0.00377111535403279</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.000274083703586348</v>
+        <v>-0.000272115686913688</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.00100091283340401</v>
+        <v>-0.000993725899929714</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.00123724600726387</v>
+        <v>-0.0012283621000424</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0050358991789249</v>
+        <v>0.00499974076772713</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.00031206450913015</v>
+        <v>-0.000312951305399024</v>
       </c>
       <c r="W32" t="n">
-        <v>0.00909886843745058</v>
+        <v>0.00933624150089906</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.0227902971602149</v>
+        <v>-0.0298915173504706</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.128004915214177</v>
+        <v>-0.126835572048354</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.163316702846099</v>
+        <v>-0.167265747536582</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.249483509006717</v>
+        <v>-0.352014719116348</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.0388590418499953</v>
+        <v>-0.0443627604894977</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.288445657970427</v>
+        <v>-0.396543429923101</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.136833557275484</v>
+        <v>0.0315223215949262</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.579767276030702</v>
+        <v>-0.690644749508038</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.590442907196101</v>
+        <v>-0.728170673111381</v>
       </c>
     </row>
     <row r="33">
@@ -7134,31 +7134,31 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.170772730331231</v>
+        <v>-0.169133352664647</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.184381860922253</v>
+        <v>-0.188083527043338</v>
       </c>
       <c r="F33" t="n">
-        <v>0.135905537440735</v>
+        <v>0.107387972036446</v>
       </c>
       <c r="G33" t="n">
-        <v>0.00329475107119413</v>
+        <v>-0.0147603692944786</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0347507967995109</v>
+        <v>-0.0206861370582575</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.428592692173076</v>
+        <v>-0.425507689290671</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00217171732057591</v>
+        <v>0.000401573096380775</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.018858383610477</v>
+        <v>-0.0163591179734329</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.0185569558244455</v>
+        <v>-0.0184227954446534</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -7170,55 +7170,55 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00249966373451131</v>
+        <v>0.0024836546491193</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.00854649047669329</v>
+        <v>0.00612293240728007</v>
       </c>
       <c r="R33" t="n">
-        <v>0.000198241682329984</v>
+        <v>0.000196818241671932</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.000992517353348797</v>
+        <v>-0.000985390702960186</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.000239928990469917</v>
+        <v>-0.000238206216964845</v>
       </c>
       <c r="U33" t="n">
-        <v>0.00393978378670825</v>
+        <v>0.00391149544931745</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.000305401729122176</v>
+        <v>-0.000306262989633209</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0528320989080066</v>
+        <v>0.0582398443811181</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.0119661510489623</v>
+        <v>-0.0145157415596074</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.194375766997843</v>
+        <v>-0.192566894759629</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.160778824255641</v>
+        <v>-0.164649984948355</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.251726694949662</v>
+        <v>-0.352799977387479</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0171152561285791</v>
+        <v>0.0201478063545492</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.234565559071119</v>
+        <v>-0.33257653716945</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.176865997223414</v>
+        <v>0.0727077119031927</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.589720150324603</v>
+        <v>-0.689793416877435</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.640206452413406</v>
+        <v>-0.767843799340733</v>
       </c>
     </row>
     <row r="34">
@@ -7232,31 +7232,31 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.203682441094879</v>
+        <v>-0.201727138018337</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.183465051487523</v>
+        <v>-0.187148311663429</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.013293126608685</v>
+        <v>-0.0405507705417563</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00134440690092982</v>
+        <v>-0.016568296371735</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0165170724095191</v>
+        <v>-0.0378804168965183</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.61669874170763</v>
+        <v>-0.271971023663552</v>
       </c>
       <c r="J34" t="n">
-        <v>0.006312814060857</v>
+        <v>0.00455684634141345</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.111062004002157</v>
+        <v>-0.109776358345879</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.0181458298110516</v>
+        <v>-0.0180146420449745</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -7268,16 +7268,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.00213178050860806</v>
+        <v>0.002154110102286</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.00341920791714002</v>
+        <v>0.00107879481530228</v>
       </c>
       <c r="R34" t="n">
-        <v>0.000194306525746327</v>
+        <v>0.000192911340845583</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.000995504968800454</v>
+        <v>-0.000988356866040734</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -7286,74 +7286,136 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.000299339828728865</v>
+        <v>-0.000300180409267764</v>
       </c>
       <c r="W34" t="n">
-        <v>0.0750876447113271</v>
+        <v>0.0843385261731741</v>
       </c>
       <c r="X34" t="n">
-        <v>0.00577189183083751</v>
+        <v>0.00924040599673284</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.226594695231705</v>
+        <v>-0.224474862324874</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.160552797350697</v>
+        <v>-0.164400587356892</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.60574419090177</v>
+        <v>-0.362700926260446</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.0438103805367445</v>
+        <v>-0.0319760637157266</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.64983686330003</v>
+        <v>-0.394800336901194</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.0109545508058604</v>
+        <v>-0.0907299025968942</v>
       </c>
       <c r="AE34" t="n">
-        <v>-1.03698435588243</v>
+        <v>-0.783675786582959</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.710543045388177</v>
+        <v>-0.756951519389169</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
         <v>67</v>
       </c>
-      <c r="B35"/>
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
+      <c r="B35" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.167253438624709</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.182973758557106</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.0607430643266406</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0111408288680098</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.0387741365338265</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.210460491391134</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.00397732415813419</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.0959908013277815</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.0176357587670267</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.00112679555396072</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-0.000903602320397778</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.000188809393181703</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-0.000582435896328418</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>-0.000293799517993503</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.109482182742921</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.0327521534465568</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>-0.304974127595372</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-0.0452530695864433</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-0.295058355791154</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.0282596989648217</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>-0.266709809192369</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>-0.0845978644000198</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>-0.616937006374184</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>-0.695262739835654</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9564,16 +9626,16 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="24">
@@ -9669,7 +9731,7 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="25">
@@ -9765,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="26">
@@ -9789,7 +9851,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0637196946742285</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -9846,22 +9908,22 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.063391363791157</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.123437717248687</v>
+        <v>0.06</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.063391363791157</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.123437717248686</v>
+        <v>0.0600000000000001</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.019140570687828</v>
+        <v>-0.035</v>
       </c>
     </row>
     <row r="27">
@@ -9870,34 +9932,34 @@
       </c>
       <c r="B27"/>
       <c r="C27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.144223857826331</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.074444414050149</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.155393852667034</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0737117668988683</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.030045383992937</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.00433793201202098</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.00342529012914509</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.08517563428052</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.0146473281668872</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -9909,55 +9971,55 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.00362045222817115</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.00767603760453444</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.0000819314314345898</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.000396038370985289</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.000270064058281161</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0000477014199298602</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.000426343830705408</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.014877548331458</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.0564584148090379</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.268872150679567</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.199092706903385</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.197246815274934</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.182973118050514</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.04409631611099</v>
+        <v>0.06</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.201584747286955</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.11387575988717</v>
+        <v>0.06</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.0593283692839645</v>
+        <v>0.0300000000000002</v>
       </c>
     </row>
     <row r="28">
@@ -9969,31 +10031,31 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00255049901370402</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.003535959880792</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.105717231891926</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0378231880751168</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.044590630423655</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.000559154252815108</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0019120624459789</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.019246265285197</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.000152243497254203</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -10005,55 +10067,55 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.00019414704049881</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.00343136419525228</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.00002016659517493</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.00004795297986134</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0000412120427124496</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.0000305830653156303</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.000062386037275439</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.05052862093931</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.0077579009788943</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.00266691244609302</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.003652373313181</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.190342553051405</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.0745753112136268</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.176027889953668</v>
+        <v>0.06</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.189783398798589</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.177013350820755</v>
+        <v>0.06</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.103581706989153</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="29">
@@ -10065,31 +10127,31 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.001018686019608</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.00401167874545699</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0710861980969855</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0186964152442417</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0584439969295432</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.000375472991987397</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.00191015274054507</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.019352564813661</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.000165272424618199</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -10101,55 +10163,55 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.000111938933861491</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.0031876324160157</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.00000210353055980105</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0000217405447869999</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.0000227158406325002</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.000061956116191841</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.000021255620010426</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.052094914614355</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.0038813874422903</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.00130337690993698</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.004296369635787</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.149930685909283</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.0724550316734608</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.137441949778797</v>
+        <v>0.06</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.150306158901271</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.140434942504647</v>
+        <v>0.0599999999999999</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.138690442615314</v>
+        <v>0.0599999999999997</v>
       </c>
     </row>
     <row r="30">
@@ -10161,31 +10223,31 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00108635629918799</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.00373616281740799</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.003898477000775</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0184229381038782</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0576670661345005</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.00191861146882299</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.00184844235928608</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0199103833741274</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0001171715342442</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -10197,55 +10259,55 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0000795133315515603</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.00292327496322324</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.00000205277070272397</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.00000966748193749999</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.00001277383961376</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.0000170424511344303</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.00002085495548026</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0546091188958319</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.0008251795498441</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.001280028468059</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.003929834986279</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.080371304065501</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.0709787459976445</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.068957115887643</v>
+        <v>0.06</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.082289915534323</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.071606922405864</v>
+        <v>0.0599999999999999</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.125732743904609</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="31">
@@ -10257,31 +10319,31 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00092959442090651</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.00362634759767702</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.00495744475019401</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0182349492347979</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0569947024135787</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.00261705505969301</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.00180201242856536</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.0603833914211819</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0001409771830128</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -10293,55 +10355,55 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.00023951620722943</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.00250894897006694</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.00000200709278481298</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.00000730363661288996</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0.00001074876173092</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0.00000232470075576402</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.00003995745551873</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.0470984899937227</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.0245890518056035</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.001114678931128</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.003811432107897</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.079795503984116</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.0850465680366011</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.225294972096503</v>
+        <v>0.0600000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.0824125590438092</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.227991725273273</v>
+        <v>0.0599999999999999</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.154261735251135</v>
+        <v>0.0600000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -10353,31 +10415,31 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.000992749250062</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.00377245077472402</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0286398295773593</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0181286470349165</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0564179079893009</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.00278002557092705</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.00175852315772141</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0035534693677482</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.000137583703094701</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -10389,55 +10451,55 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.000146862953884806</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.00245770286128456</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.00000196801667265998</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00000718693347429586</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.00000888390722147015</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.00003615841119777</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.000000886796268873989</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.00023737306344848</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.0071012201902557</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.00116934316582301</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.00394904469048299</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.102531210109631</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.0055037186395024</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.108097771952674</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.105311235680558</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.110877473477336</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.13772776591528</v>
+        <v>0.0449999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -10449,31 +10511,31 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00163937766658401</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.003701666121085</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.028517565404289</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0180551203656727</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.0554369338577684</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.00308500288240499</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.00177014422419514</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0024992656370441</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.000134160379792102</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -10485,55 +10547,55 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.0000160090853920099</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.00242355806941322</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.000001423440658052</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.00000712665038861112</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.00000172277350507201</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.0000282883373908006</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.000000861260511032997</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0054077454731115</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.0025495905106451</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.00180887223821402</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.00387116069271401</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.101073282437817</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0030325502259701</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.098010978098331</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.104158285320221</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.100073266552832</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.127637346927327</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="34">
@@ -10545,31 +10607,31 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00195530307654201</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.00368326017590598</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0272576439330713</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0179127032726648</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.0543974893060374</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.344727718044078</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.00175596771944355</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.00128564565627801</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.000131187766077099</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -10581,16 +10643,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0000223295936779399</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.00234041310183774</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.000001395184900744</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.00000714810275972001</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -10599,37 +10661,37 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.000000840580538898962</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0.00925088146184699</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.00346851416589533</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.00211983290683099</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.00384779000619501</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.243043264641324</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.0118343168210179</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.255036526398836</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.101684453402755</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.253308569299471</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.046408474000992</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="35">
@@ -10637,36 +10699,96 @@
         <v>67</v>
       </c>
       <c r="B35"/>
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
